--- a/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X84"/>
+  <dimension ref="A1:X86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,32 +633,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688856736832479</t>
+          <t>1688856644818249</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>曹钰淼</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>caoyumiao</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -670,29 +670,24 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,20,21</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>曹钰淼</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>caoyumiao</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -737,32 +732,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688855270890470</t>
+          <t>1688854894759558</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -774,29 +769,24 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -841,32 +831,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688855270890478</t>
+          <t>1688857605746717</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>朱鑫磊</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zhuxinlei</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -878,11 +868,11 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -890,17 +880,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>朱鑫磊</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>zhuxinlei</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -945,32 +935,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688857392814199</t>
+          <t>1688854522753923</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -985,21 +975,26 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>17,23</t>
+        </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1044,32 +1039,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688858124858984</t>
+          <t>1688858289869798</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1081,29 +1076,24 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1148,32 +1138,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688855928851644</t>
+          <t>1688855270890428</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>刘佳宁</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>liujianing</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1185,24 +1175,29 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>刘佳宁</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>liujianing</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1247,32 +1242,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688857254754511</t>
+          <t>1688857455845397</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1284,24 +1279,29 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10,11,12,13,14,15,16,17,18</t>
+        </is>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688855639780332</t>
+          <t>1688857609868354</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1445,32 +1445,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688855086834341</t>
+          <t>1688854281870550</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688857752769746</t>
+          <t>1688855270890461</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1559,17 +1559,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>魏布婷</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>weibuting</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1581,7 +1581,12 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1593,12 +1598,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>魏布婷</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>weibuting</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1643,32 +1648,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688854287853916</t>
+          <t>1688858124858984</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1680,11 +1685,11 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1692,17 +1697,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1747,7 +1752,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688856312814793</t>
+          <t>1688858124858856</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1757,22 +1762,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1796,12 +1801,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1846,7 +1851,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688857691776053</t>
+          <t>1688858199721276</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1861,17 +1866,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1895,12 +1900,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1945,32 +1950,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688855770825227</t>
+          <t>1688857691776053</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>梁秀枝</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>liangxiuzhi</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1982,29 +1987,24 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>梁秀枝</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>liangxiuzhi</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688855270890428</t>
+          <t>1688857751871196</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>刘佳宁</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>liujianing</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2083,28 +2083,13 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2113,12 +2098,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>刘佳宁</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>liujianing</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2163,32 +2148,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688855270890461</t>
+          <t>1688854476856492</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>魏布婷</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>weibuting</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2200,29 +2185,24 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>魏布婷</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>weibuting</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2267,32 +2247,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688854281870561</t>
+          <t>1688855564781214</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2304,29 +2284,24 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2371,7 +2346,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688854497763364</t>
+          <t>1688854287853876</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2381,22 +2356,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2408,7 +2383,12 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -2420,12 +2400,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2470,32 +2450,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688857703847806</t>
+          <t>1688857751871176</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>吕怡萱</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>lvyixuan</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2507,29 +2487,24 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>吕怡萱</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>lvyixuan</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2574,32 +2549,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688855270890491</t>
+          <t>1688855270890478</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>朱鑫磊</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhuxinlei</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2623,17 +2598,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>朱鑫磊</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhuxinlei</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2678,7 +2653,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688858289869798</t>
+          <t>1688855639780332</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2688,22 +2663,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2727,12 +2702,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2777,7 +2752,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688854522754143</t>
+          <t>1688857392814199</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2792,17 +2767,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2826,12 +2801,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2876,32 +2851,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688854497763413</t>
+          <t>1688855928851644</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2920,17 +2895,17 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2975,32 +2950,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688854281870539</t>
+          <t>1688855270890446</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3024,17 +2999,17 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3079,7 +3054,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688858124858856</t>
+          <t>1688856624782683</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3089,22 +3064,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3116,12 +3091,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
@@ -3133,12 +3103,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3183,7 +3153,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688858124858906</t>
+          <t>1688854260743321</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3193,22 +3163,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3220,12 +3190,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
@@ -3237,12 +3202,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3287,7 +3252,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688854706800124</t>
+          <t>1688857755978271</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3297,22 +3262,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>范夺</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>fanduo</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3336,12 +3301,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>范夺</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>fanduo</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3386,32 +3351,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688857751871228</t>
+          <t>1688854281870569</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3420,32 +3385,42 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O29" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3490,7 +3465,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688857751871176</t>
+          <t>1688854497763364</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3500,22 +3475,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>吕怡萱</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>lvyixuan</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3527,12 +3502,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>17,18</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -3544,12 +3514,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>吕怡萱</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>lvyixuan</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3594,7 +3564,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688854281870569</t>
+          <t>1688854281870539</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3609,17 +3579,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3648,12 +3618,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3698,32 +3668,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688855270890512</t>
+          <t>1688855270890491</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3747,17 +3717,17 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3802,32 +3772,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688854815837469</t>
+          <t>1688854287853891</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3839,24 +3809,29 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3901,32 +3876,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688856995795370</t>
+          <t>1688854603884803</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3945,17 +3920,17 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4000,32 +3975,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688857751871196</t>
+          <t>1688855600786055</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4037,29 +4012,29 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>7,8,9,10</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4104,7 +4079,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688854522754461</t>
+          <t>1688857145762192</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4119,17 +4094,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4141,12 +4116,7 @@
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -4158,12 +4128,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4208,32 +4178,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688855593838985</t>
+          <t>1688857115860438</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4245,29 +4215,24 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4312,32 +4277,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688854470818602</t>
+          <t>1688855086834341</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4356,17 +4321,17 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4411,32 +4376,32 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688856443851784</t>
+          <t>1688856312814793</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>蒋明阳</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>jiangmingyang</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4451,26 +4416,21 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>蒋明阳</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>jiangmingyang</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4515,32 +4475,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688855581862225</t>
+          <t>1688854706799328</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4552,29 +4512,24 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4619,32 +4574,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688854894759300</t>
+          <t>1688855770825630</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4663,17 +4618,17 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4718,32 +4673,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688854776688740</t>
+          <t>1688856443851799</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>闫刘梦</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>yanliumeng</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4755,24 +4710,29 @@
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>闫刘梦</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>yanliumeng</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4817,32 +4777,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688855270890436</t>
+          <t>1688856736832479</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>曹钰淼</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>caoyumiao</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4854,11 +4814,11 @@
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>22,23</t>
         </is>
       </c>
       <c r="Q43" t="n">
@@ -4866,17 +4826,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>曹钰淼</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>caoyumiao</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4921,32 +4881,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688857455845397</t>
+          <t>1688855581862225</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4958,11 +4918,11 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="Q44" t="n">
@@ -4970,17 +4930,17 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5025,7 +4985,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688857605746717</t>
+          <t>1688857372708211</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5040,17 +5000,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5062,12 +5022,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -5079,12 +5034,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5129,7 +5084,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688857372708211</t>
+          <t>1688857452809589</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5139,22 +5094,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5178,12 +5133,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5228,32 +5183,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688855270890446</t>
+          <t>1688854522754361</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5265,11 +5220,11 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -5277,17 +5232,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5332,32 +5287,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688854287853891</t>
+          <t>1688856443851784</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>蒋明阳</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>jiangmingyang</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5369,29 +5324,29 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0</v>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>蒋明阳</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>jiangmingyang</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5436,32 +5391,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688857609868354</t>
+          <t>1688854522754461</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5473,24 +5428,29 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5535,32 +5495,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688854476856420</t>
+          <t>1688855473818358</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5575,26 +5535,21 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5639,7 +5594,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688855070755789</t>
+          <t>1688856475868784</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5649,22 +5604,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5676,12 +5631,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -5693,12 +5643,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5743,32 +5693,32 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688855473818358</t>
+          <t>1688854706800124</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5787,17 +5737,17 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5842,7 +5792,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688854281870550</t>
+          <t>1688855270890470</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5857,17 +5807,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5879,20 +5829,15 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>8,9,10,11,14,22</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5901,12 +5846,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5951,7 +5896,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688854287853876</t>
+          <t>1688857254754511</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5961,22 +5906,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5988,12 +5933,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
@@ -6005,12 +5945,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6055,32 +5995,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688855827846478</t>
+          <t>1688857752769746</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6099,17 +6039,17 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6154,7 +6094,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688854761929635</t>
+          <t>1688854281870599</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6164,22 +6104,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6203,12 +6143,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6253,32 +6193,32 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688855600786055</t>
+          <t>1688858124858906</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6290,29 +6230,29 @@
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q57" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6357,32 +6297,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688857115860438</t>
+          <t>1688854572834470</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6401,17 +6341,17 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6456,32 +6396,32 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688857145762192</t>
+          <t>1688855770825227</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>梁秀枝</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>liangxiuzhi</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6493,11 +6433,11 @@
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>13,14,15,16</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -6505,17 +6445,17 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>梁秀枝</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>liangxiuzhi</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6560,32 +6500,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688856443851799</t>
+          <t>1688854281870561</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>闫刘梦</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>yanliumeng</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6597,11 +6537,11 @@
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -6609,17 +6549,17 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>闫刘梦</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>yanliumeng</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6664,7 +6604,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688854894759558</t>
+          <t>1688855270890512</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6674,22 +6614,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6701,7 +6641,12 @@
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -6713,12 +6658,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6763,32 +6708,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688854281870599</t>
+          <t>1688855270890436</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6800,29 +6745,34 @@
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>6,7,8,9,10</t>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>17,20</t>
+        </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6867,32 +6817,32 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688854706799328</t>
+          <t>1688854761929635</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6911,17 +6861,17 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6966,7 +6916,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688856644818249</t>
+          <t>1688854776688740</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6981,17 +6931,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -7006,7 +6956,12 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>15,22</t>
+        </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -7015,12 +6970,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -7065,7 +7020,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688854476856492</t>
+          <t>1688854287853916</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7075,22 +7030,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7102,7 +7057,12 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
@@ -7114,12 +7074,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7164,32 +7124,32 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688856819940740</t>
+          <t>1688854497763413</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7208,17 +7168,17 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7263,32 +7223,32 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688855292870141</t>
+          <t>1688854476856420</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7300,29 +7260,29 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7367,32 +7327,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688854522754361</t>
+          <t>1688854894759300</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7411,17 +7371,17 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7466,32 +7426,32 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688857452809589</t>
+          <t>1688855292870141</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7503,24 +7463,29 @@
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14</t>
+        </is>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7560,42 +7525,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>初中</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688854894759430</t>
+          <t>1688857951732153</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -7609,17 +7574,17 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7664,7 +7629,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688856920865401</t>
+          <t>1688857703847806</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7674,22 +7639,22 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7701,7 +7666,12 @@
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
@@ -7713,12 +7683,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7763,32 +7733,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688854260743321</t>
+          <t>1688854522754143</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7807,17 +7777,17 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7862,32 +7832,32 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688854522753923</t>
+          <t>1688854815837469</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7906,17 +7876,17 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7956,37 +7926,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>初中</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688854572834470</t>
+          <t>1688857951732153</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -8005,17 +7975,17 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -8060,7 +8030,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688855564781214</t>
+          <t>1688858275775684</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8070,22 +8040,22 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8097,7 +8067,12 @@
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
@@ -8109,12 +8084,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8159,32 +8134,32 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688856475868784</t>
+          <t>1688854470818602</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8203,17 +8178,17 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -8258,32 +8233,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688854603884803</t>
+          <t>1688858008853709</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8302,17 +8277,17 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -8357,7 +8332,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688857755978271</t>
+          <t>1688854894759430</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -8367,22 +8342,22 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>范夺</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>fanduo</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8397,12 +8372,7 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -8411,12 +8381,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>范夺</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>fanduo</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -8461,32 +8431,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688856624782683</t>
+          <t>1688855593838985</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8505,17 +8475,17 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -8560,32 +8530,32 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688855770825630</t>
+          <t>1688856995795370</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8597,29 +8567,24 @@
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>21,22</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8664,32 +8629,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688858275775684</t>
+          <t>1688855827846478</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8701,24 +8666,34 @@
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="Q81" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>22,23</t>
+        </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8763,7 +8738,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1688858199721276</t>
+          <t>1688857751871228</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8778,17 +8753,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8797,13 +8772,28 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8812,12 +8802,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8862,32 +8852,32 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1688858008853709</t>
+          <t>1688856920865401</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8899,24 +8889,29 @@
         <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="Q83" t="n">
         <v>1</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8976,7 +8971,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9029,6 +9024,209 @@
         </is>
       </c>
       <c r="X84" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>20260911</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1688855070755789</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>严绍源</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>yanshaoyuan</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>严绍源</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>yanshaoyuan</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>20260911</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1688856819940740</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>芦凯</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>lukai</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>芦凯</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>lukai</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -9045,7 +9243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9110,16 +9308,16 @@
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="3">
@@ -9138,16 +9336,16 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="4">
@@ -9170,10 +9368,10 @@
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="G4" t="n">
         <v>8</v>
@@ -9202,16 +9400,16 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="6">
@@ -9230,16 +9428,16 @@
         <v>25</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -9259,19 +9457,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8666666666666667</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -9332,10 +9530,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="10">
@@ -9351,19 +9549,19 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="11">
@@ -9383,19 +9581,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="12">
@@ -9406,24 +9604,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>新兵营 汇总</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>蒸蒸日上-兴-刘亚雄</t>
+        </is>
+      </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5263157894736842</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3157894736842105</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -9434,24 +9636,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>初中 汇总</t>
+          <t>新兵营 汇总</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5274725274725275</v>
+        <v>0.3157894736842105</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>初中 汇总</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E14" t="n">
+        <v>75</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G14" t="n">
+        <v>53</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5888888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -9465,7 +9695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9481,7 +9711,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄初短）-9月9日</t>
+          <t>企微风灵全天在线情况通晒（石家庄初短）-9月10日</t>
         </is>
       </c>
     </row>
@@ -9565,16 +9795,16 @@
         <v>11</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="5">
@@ -9593,16 +9823,16 @@
         <v>11</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="6">
@@ -9625,10 +9855,10 @@
         <v>14</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>8</v>
@@ -9657,16 +9887,16 @@
         <v>11</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="8">
@@ -9685,16 +9915,16 @@
         <v>25</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -9714,19 +9944,19 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.8666666666666667</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="10">
@@ -9787,10 +10017,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="12">
@@ -9806,19 +10036,19 @@
       </c>
       <c r="C12" s="6" t="inlineStr"/>
       <c r="D12" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="13">
@@ -9838,47 +10068,51 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.2777777777777778</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>新兵营 汇总</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>0.5263157894736842</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>0.3157894736842105</v>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>蒸蒸日上-兴-刘亚雄</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -9889,24 +10123,52 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>初中 汇总</t>
+          <t>新兵营 汇总</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr"/>
       <c r="D15" s="6" t="n">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.5274725274725275</v>
+        <v>0.3157894736842105</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>初中 汇总</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0.5888888888888889</v>
       </c>
     </row>
   </sheetData>
